--- a/data/input/feed/baci/current/conc.xlsx
+++ b/data/input/feed/baci/current/conc.xlsx
@@ -889,7 +889,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -910,7 +909,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1081,7 +1079,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1102,7 +1099,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1298,7 +1294,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1369,7 +1364,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1415,7 +1409,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1586,7 +1579,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1682,7 +1674,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1703,7 +1694,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1724,7 +1714,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1745,7 +1734,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2116,7 +2104,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2512,7 +2499,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2608,7 +2594,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2754,7 +2739,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2825,7 +2809,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3121,7 +3104,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -3142,7 +3124,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3163,7 +3144,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3259,7 +3239,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3305,7 +3284,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3351,7 +3329,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -3647,7 +3624,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3718,7 +3694,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3839,7 +3814,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3910,7 +3884,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -3931,7 +3904,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -4177,7 +4149,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -4198,7 +4169,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -4456,12 +4426,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ROW</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>aggregate</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4471,7 +4441,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Corrected from 'RoW'</t>
+          <t>'Other Asia, nes' is Taiwan's trade in UN Comtrade and BACI; was ROW (#77)</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4514,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -4565,7 +4534,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -4611,7 +4579,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -4632,7 +4599,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -4678,7 +4644,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -4699,7 +4664,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -5270,7 +5234,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -5291,7 +5254,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -5387,7 +5349,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -5458,7 +5419,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -5604,7 +5564,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -5625,7 +5584,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -6021,7 +5979,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -6042,7 +5999,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -6188,7 +6144,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -6334,7 +6289,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -7052,7 +7006,6 @@
           <t>src_time</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>cast to str → time_map</t>
@@ -7080,7 +7033,6 @@
           <t>src_sector_from</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>direct → sector_map (HS code)</t>
@@ -7108,7 +7060,6 @@
           <t>src_region_from</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>direct → region_map (numeric ID)</t>
@@ -7136,7 +7087,6 @@
           <t>src_region_to</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>direct → region_map (numeric ID)</t>
@@ -7164,7 +7114,6 @@
           <t>src_valuation</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>direct → valuation_map</t>

--- a/data/input/feed/baci/current/conc.xlsx
+++ b/data/input/feed/baci/current/conc.xlsx
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>'Other Asia, nes' is Taiwan's trade in UN Comtrade and BACI; was ROW (#77)</t>
+          <t>'Other Asia, nes' is Taiwan's trade in UN Comtrade and BACI; its cathode imports track ICSG's Taiwan usage (#77); was ROW</t>
         </is>
       </c>
     </row>

--- a/data/input/feed/baci/current/conc.xlsx
+++ b/data/input/feed/baci/current/conc.xlsx
@@ -1841,12 +1841,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ROW</t>
+          <t>Congo, D.R.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>aggregate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Corrected from 'RoW'</t>
+          <t>BACI's 'Congo' carries DR Congo's cathode: 3,890 kt exported in 2012–2024 against Brazzaville's 79 kt of ICSG production and DR Congo's shortfall under 180 (#84); was ROW</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5381,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ROW</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>aggregate</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Corrected from 'RoW'</t>
+          <t>'Southern African Customs Union' is South Africa's trade until BACI splits it in 2000; Namibia's anode and Botswana's matte ride with it (#84); was ROW</t>
         </is>
       </c>
     </row>

--- a/data/input/feed/baci/current/conc.xlsx
+++ b/data/input/feed/baci/current/conc.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,6 +551,66 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>Copper cathodes and sections of cathodes unwrought</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>740312</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cathode</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Copper wire-bars, refined, unwrought (#91)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>740313</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cathode</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Copper billets, refined, unwrought (#91)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>740319</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cathode</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Other refined copper, unwrought (#91)</t>
         </is>
       </c>
     </row>
